--- a/documentacao/Testes/Caso de Teste/UC10 - MANTER PERFIL.xlsx
+++ b/documentacao/Testes/Caso de Teste/UC10 - MANTER PERFIL.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IFCE\Documents\GitHub\taximix\chekout\plataformainclua\documentacao\Testes\Caso de Teste\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C82BFB6-70C6-47F6-B820-F7CB4ACA8E00}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Casos de Teste" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,194 +25,179 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
-  <si>
-    <t xml:space="preserve">Caso de Teste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objetivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pré-Condições</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados de Entrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado Esperado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado Obtido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status (OK/NOK)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT01 - Acessar Página de Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar exibição dos dados do perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usuário autenticado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar em "Meu Perfil"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exibir nome, e-mail, foto e dados cadastrais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todos os campos exibidos corretamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT02 - Editar Nome com Sucesso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validar atualização do nome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfil carregado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar "Editar"
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+  <si>
+    <t>Caso de Teste</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Pré-Condições</t>
+  </si>
+  <si>
+    <t>Passos</t>
+  </si>
+  <si>
+    <t>Dados de Entrada</t>
+  </si>
+  <si>
+    <t>Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Resultado Obtido</t>
+  </si>
+  <si>
+    <t>Status (OK/NOK)</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>CT01 - Acessar Página de Perfil</t>
+  </si>
+  <si>
+    <t>Verificar exibição dos dados do perfil</t>
+  </si>
+  <si>
+    <t>Usuário autenticado</t>
+  </si>
+  <si>
+    <t>1. Clicar em "Meu Perfil"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Exibir nome, e-mail, foto e dados cadastrais</t>
+  </si>
+  <si>
+    <t>Todos os campos exibidos corretamente</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>CT02 - Editar Nome com Sucesso</t>
+  </si>
+  <si>
+    <t>Validar atualização do nome</t>
+  </si>
+  <si>
+    <t>Perfil carregado</t>
+  </si>
+  <si>
+    <t>1. Clicar "Editar"
 2. Alterar nome
 3. Salvar</t>
   </si>
   <si>
-    <t xml:space="preserve">Nome: "Ana → Ana Silva"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome atualizado no sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alteração refletida imediatamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT06 - Upload Foto Válida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testar envio de imagem correta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfil editável</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar "Alterar Foto"
+    <t>Nome: "Ana → Ana Silva"</t>
+  </si>
+  <si>
+    <t>Nome atualizado no sistema</t>
+  </si>
+  <si>
+    <t>Alteração refletida imediatamente</t>
+  </si>
+  <si>
+    <t>CT06 - Upload Foto Válida</t>
+  </si>
+  <si>
+    <t>Testar envio de imagem correta</t>
+  </si>
+  <si>
+    <t>Perfil editável</t>
+  </si>
+  <si>
+    <t>1. Clicar "Alterar Foto"
 2. Selecionar arquivo</t>
   </si>
   <si>
-    <t xml:space="preserve">"foto.jpg" (1.5MB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thumbnail atualizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagem processada corretamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT07 - Tentar Arquivo Inválido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validar restrições de formato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em edição de foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Selecionar PDF
+    <t>"foto.jpg" (1.5MB)</t>
+  </si>
+  <si>
+    <t>Thumbnail atualizado</t>
+  </si>
+  <si>
+    <t>Imagem processada corretamente</t>
+  </si>
+  <si>
+    <t>CT07 - Tentar Arquivo Inválido</t>
+  </si>
+  <si>
+    <t>Validar restrições de formato</t>
+  </si>
+  <si>
+    <t>Em edição de foto</t>
+  </si>
+  <si>
+    <t>1. Selecionar PDF
 2. Tentar enviar</t>
   </si>
   <si>
-    <t xml:space="preserve">"doc.pdf"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem "Apenas JPG/PNG"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro exibido corretamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT08 - Desativar Conta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar fluxo de inativação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Configurações
+    <t>"doc.pdf"</t>
+  </si>
+  <si>
+    <t>Mensagem "Apenas JPG/PNG"</t>
+  </si>
+  <si>
+    <t>Erro exibido corretamente</t>
+  </si>
+  <si>
+    <t>CT08 - Desativar Conta</t>
+  </si>
+  <si>
+    <t>Verificar fluxo de inativação</t>
+  </si>
+  <si>
+    <t>1. Configurações
 2. "Desativar Conta"
 3. Confirmar</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmação e logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conta marcada como inativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT10 - Validar Campos Obrigatórios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar preenchimento mínimo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em edição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Apagar nome
+    <t>Confirmação e logout</t>
+  </si>
+  <si>
+    <t>Conta marcada como inativa</t>
+  </si>
+  <si>
+    <t>CT10 - Validar Campos Obrigatórios</t>
+  </si>
+  <si>
+    <t>Verificar preenchimento mínimo</t>
+  </si>
+  <si>
+    <t>Em edição</t>
+  </si>
+  <si>
+    <t>1. Apagar nome
 2. Tentar salvar</t>
   </si>
   <si>
-    <t xml:space="preserve">Nome: ""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destaque no campo vazio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem "Campo obrigatório"</t>
+    <t>Nome: ""</t>
+  </si>
+  <si>
+    <t>Destaque no campo vazio</t>
+  </si>
+  <si>
+    <t>Mensagem "Campo obrigatório"</t>
+  </si>
+  <si>
+    <t>V2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -217,7 +207,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -234,7 +239,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -242,115 +247,93 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -403,25 +386,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AMJ7"/>
+  <sheetFormatPr defaultColWidth="32.21875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="49.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="32.22"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="49.33203125" style="1" customWidth="1"/>
+    <col min="5" max="1024" width="32.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -449,8 +431,11 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" ht="30.75">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -478,8 +463,11 @@
       <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="J2" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10" ht="45.75">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -507,8 +495,11 @@
       <c r="I3" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="J3" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10" ht="30.75">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -536,8 +527,11 @@
       <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="J4" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:10" ht="30.75">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -565,8 +559,11 @@
       <c r="I5" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="J5" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10" ht="45.75">
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
@@ -594,8 +591,11 @@
       <c r="I6" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="J6" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" ht="31.5">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -623,15 +623,12 @@
       <c r="I7" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="J7" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>